--- a/Phytium_PPE_System_SourceCode/04_风险管理闭环设计报告_终稿.xlsx
+++ b/Phytium_PPE_System_SourceCode/04_风险管理闭环设计报告_终稿.xlsx
@@ -456,12 +456,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>基于AMP架构，主核(Linux)增加心跳发送模块，从核(RTOS/裸机)配置飞腾硬件看门狗(FWDT)。若从核监控不到主核心跳，立刻触发硬件看门狗介入并控制蜂鸣器持续告警。</t>
+          <t>基于AMP架构，主核(Linux)增加心跳发送模块，从核(RTOS/裸机)配置飞腾硬件看门狗(FWDT)。若从核监控不到主核心跳，立刻触发硬件看门狗介入。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>在主控程序引入死循环或段错误故障，验证从核是否能准确检测心跳超时并发出硬件级停止/告警信号。</t>
+          <t>在主控程序引入死循环或段错误故障，验证从核是否能准确检测心跳超时并发出硬件级停止信号。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
